--- a/it_forms/004_website_malware_monitoring_checklist--it_forms.xlsx
+++ b/it_forms/004_website_malware_monitoring_checklist--it_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -912,12 +912,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C19"/>
+  <dimension ref="A1:C14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="27" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="28" customWidth="1" min="2" max="2"/>
+    <col width="28" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -945,12 +945,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_true}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': True}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -962,12 +962,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_false}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': False}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -979,12 +979,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_true}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': True}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -996,12 +996,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_false}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': False}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -1013,12 +1013,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'sql_injection'}</t>
+          <t>sql_injection</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'SQL Injection'}</t>
+          <t>SQL Injection</t>
         </is>
       </c>
     </row>
@@ -1030,216 +1030,131 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'cross-site_scripting_(xss)'}</t>
+          <t>cross-site_scripting_(xss)</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Cross-Site Scripting (XSS)'}</t>
+          <t>Cross-Site Scripting (XSS)</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>malware_type_choices</t>
+          <t>detection_method_choices</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'cross-site_scripting_(xss)'}</t>
+          <t>automated_tool</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Cross-Site Scripting (XSS)'}</t>
+          <t>Automated Tool</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>malware_type_choices</t>
+          <t>detection_method_choices</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_4,_'label':_'cross-site_scripting_(xss)'}</t>
+          <t>manual_check</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 4, 'label': 'Cross-Site Scripting (XSS)'}</t>
+          <t>Manual Check</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>malware_type_choices</t>
+          <t>detection_method_choices</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_5,_'label':_'cross-site_scripting_(xss)'}</t>
+          <t>user_report</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': 5, 'label': 'Cross-Site Scripting (XSS)'}</t>
+          <t>User Report</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>malware_type_choices</t>
+          <t>review_frequency_choices</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'id':_6,_'label':_'cross-site_scripting_(xss)'}</t>
+          <t>daily</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'id': 6, 'label': 'Cross-Site Scripting (XSS)'}</t>
+          <t>Daily</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>malware_type_choices</t>
+          <t>review_frequency_choices</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'id':_7,_'label':_'cross-site_scripting_(xss)'}</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'id': 7, 'label': 'Cross-Site Scripting (XSS)'}</t>
+          <t>Weekly</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>detection_method_choices</t>
+          <t>review_frequency_choices</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'automated_tool'}</t>
+          <t>monthly</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Automated Tool'}</t>
+          <t>Monthly</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>detection_method_choices</t>
+          <t>review_frequency_choices</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'manual_check'}</t>
+          <t>never</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Manual Check'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>detection_method_choices</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>{'id':_3,_'label':_'user_report'}</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>{'id': 3, 'label': 'User Report'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>review_frequency_choices</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>{'id':_1,_'label':_'daily'}</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>{'id': 1, 'label': 'Daily'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>review_frequency_choices</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>{'id':_2,_'label':_'weekly'}</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>{'id': 2, 'label': 'Weekly'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>review_frequency_choices</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>{'id':_3,_'label':_'monthly'}</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>{'id': 3, 'label': 'Monthly'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>review_frequency_choices</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>{'id':_4,_'label':_'never'}</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>{'id': 4, 'label': 'Never'}</t>
+          <t>Never</t>
         </is>
       </c>
     </row>
